--- a/Timings.xlsx
+++ b/Timings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\MEP\Christof\Clear\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\MEP\RMEP_homotopy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76877D07-F857-4DA5-AB85-1F10646B1770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA18A6A-2471-474E-8208-B1277FD2816F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11772" yWindow="660" windowWidth="27060" windowHeight="15480" xr2:uid="{A4011660-FB7A-4DB9-A678-D73B0BBE67FE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A4011660-FB7A-4DB9-A678-D73B0BBE67FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="29">
   <si>
     <t>n</t>
   </si>
@@ -93,6 +93,36 @@
   </si>
   <si>
     <t>Comparison MultiParEig, MacaulayLab, homotopy for random linear RMEP</t>
+  </si>
+  <si>
+    <t>k=30</t>
+  </si>
+  <si>
+    <t>k=40</t>
+  </si>
+  <si>
+    <t>k=50</t>
+  </si>
+  <si>
+    <t>k=60</t>
+  </si>
+  <si>
+    <t>OUT OF MEM</t>
+  </si>
+  <si>
+    <t>NO GAP</t>
+  </si>
+  <si>
+    <t>* 413,72</t>
+  </si>
+  <si>
+    <t>* 4203</t>
+  </si>
+  <si>
+    <t>k=100</t>
+  </si>
+  <si>
+    <t>* 3359,03</t>
   </si>
 </sst>
 </file>
@@ -122,7 +152,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -143,13 +173,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -166,21 +226,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -495,71 +562,87 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D26378D0-B3BB-4455-B056-646B4297C753}">
-  <dimension ref="A1:AT59"/>
+  <dimension ref="A1:BJ59"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.88671875" customWidth="1"/>
-    <col min="7" max="7" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.88671875" customWidth="1"/>
+    <col min="8" max="8" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="12.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:46" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
+    <row r="3" spans="1:62" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="F3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="J3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="13" t="s">
+      <c r="N3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="Q3" s="13" t="s">
+      <c r="R3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="U3" s="13" t="s">
+      <c r="V3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="Y3" s="13" t="s">
+      <c r="Z3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="AC3" s="13" t="s">
+      <c r="AD3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="AF3" s="13" t="s">
+      <c r="AG3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AI3" s="13" t="s">
+      <c r="AJ3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="AL3" s="13" t="s">
+      <c r="AM3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="AO3" s="13" t="s">
+      <c r="AP3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="AR3" s="13" t="s">
+      <c r="AS3" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="AV3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="AY3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="BB3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="BE3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="BH3" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:62" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>17</v>
       </c>
@@ -570,134 +653,182 @@
         <v>16</v>
       </c>
       <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
         <v>17</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>8</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>16</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>9</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>17</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>8</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>16</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>9</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>17</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>8</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>16</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>17</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>8</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>16</v>
       </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
         <v>9</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>17</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
         <v>8</v>
       </c>
-      <c r="W4" t="s">
+      <c r="X4" t="s">
         <v>16</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Y4" t="s">
         <v>9</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>17</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
         <v>8</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>16</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>9</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
         <v>17</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>8</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>9</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AG4" t="s">
         <v>17</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AH4" t="s">
         <v>8</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="AI4" t="s">
         <v>9</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AJ4" t="s">
         <v>17</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AK4" t="s">
         <v>8</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AL4" t="s">
         <v>9</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AM4" t="s">
         <v>17</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="AN4" t="s">
         <v>8</v>
       </c>
-      <c r="AN4" t="s">
+      <c r="AO4" t="s">
         <v>9</v>
       </c>
-      <c r="AO4" t="s">
+      <c r="AP4" t="s">
         <v>17</v>
       </c>
-      <c r="AP4" t="s">
+      <c r="AQ4" t="s">
         <v>8</v>
       </c>
-      <c r="AQ4" t="s">
+      <c r="AR4" t="s">
         <v>9</v>
       </c>
-      <c r="AR4" t="s">
+      <c r="AS4" t="s">
         <v>17</v>
       </c>
-      <c r="AS4" t="s">
+      <c r="AT4" t="s">
         <v>8</v>
       </c>
-      <c r="AT4" t="s">
+      <c r="AU4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:46" x14ac:dyDescent="0.3">
-      <c r="A5" s="13">
+      <c r="AV4" t="s">
+        <v>17</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>9</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>17</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>9</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>17</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>9</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>17</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BG4" t="s">
+        <v>9</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>17</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <v>2</v>
       </c>
       <c r="B5">
@@ -706,135 +837,180 @@
       <c r="C5" s="6">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="9">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="3"/>
+      <c r="F5">
         <v>4</v>
       </c>
-      <c r="F5" s="6">
+      <c r="G5" s="6">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="G5" s="7">
+      <c r="H5" s="9">
         <v>1.9E-3</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="11"/>
+      <c r="J5">
         <v>5</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="12">
         <v>4.1000000000000003E-3</v>
       </c>
-      <c r="K5">
+      <c r="L5" s="4">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="L5">
+      <c r="M5" s="11">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>6</v>
       </c>
-      <c r="N5" s="3">
+      <c r="O5" s="4">
         <v>5.1999999999999998E-3</v>
       </c>
-      <c r="O5">
+      <c r="P5" s="11">
         <v>4.1599999999999998E-2</v>
       </c>
-      <c r="P5">
+      <c r="Q5" s="10">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="Q5">
+      <c r="R5">
         <v>7</v>
       </c>
-      <c r="R5" s="3">
+      <c r="S5" s="4">
         <v>7.6E-3</v>
       </c>
-      <c r="S5">
+      <c r="T5" s="11">
         <v>0.27</v>
       </c>
-      <c r="T5">
+      <c r="U5" s="12">
         <v>0.04</v>
       </c>
-      <c r="U5">
+      <c r="V5">
         <v>8</v>
       </c>
-      <c r="V5" s="3">
-        <v>8.5000000000000006E-3</v>
-      </c>
-      <c r="W5" s="1">
-        <v>2.36</v>
-      </c>
-      <c r="X5" s="1">
-        <v>3.7999999999999999E-2</v>
-      </c>
-      <c r="Y5">
+      <c r="W5" s="4">
+        <v>1.3899999999999999E-2</v>
+      </c>
+      <c r="X5" s="17">
+        <v>2.3860000000000001</v>
+      </c>
+      <c r="Y5" s="18">
+        <v>6.5600000000000006E-2</v>
+      </c>
+      <c r="Z5">
         <v>9</v>
       </c>
-      <c r="Z5" s="3">
+      <c r="AA5" s="4">
         <v>0.01</v>
       </c>
-      <c r="AA5">
+      <c r="AB5" s="11">
         <v>28.82</v>
       </c>
-      <c r="AB5">
+      <c r="AC5" s="10">
         <v>0.06</v>
       </c>
-      <c r="AC5">
+      <c r="AD5">
         <v>10</v>
       </c>
-      <c r="AD5" s="3">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="AE5">
-        <v>0.06</v>
-      </c>
-      <c r="AF5">
+      <c r="AE5" s="4">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AF5" s="10">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="AG5">
         <v>11</v>
       </c>
-      <c r="AG5" s="3">
-        <v>1.32E-2</v>
-      </c>
-      <c r="AH5">
-        <v>0.16</v>
-      </c>
-      <c r="AI5">
+      <c r="AH5" s="4">
+        <v>2.7199999999999998E-2</v>
+      </c>
+      <c r="AI5" s="16">
+        <v>9.9400000000000002E-2</v>
+      </c>
+      <c r="AJ5">
         <v>12</v>
       </c>
-      <c r="AJ5" s="3">
-        <v>1.6E-2</v>
-      </c>
-      <c r="AK5">
-        <v>0.08</v>
-      </c>
-      <c r="AL5">
+      <c r="AK5" s="4">
+        <v>3.1199999999999999E-2</v>
+      </c>
+      <c r="AL5" s="10">
+        <v>0.121</v>
+      </c>
+      <c r="AM5">
         <v>13</v>
       </c>
-      <c r="AM5" s="3">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="AN5">
-        <v>0.123</v>
-      </c>
-      <c r="AO5">
+      <c r="AN5" s="4">
+        <v>3.5099999999999999E-2</v>
+      </c>
+      <c r="AO5" s="10">
+        <v>0.128</v>
+      </c>
+      <c r="AP5">
         <v>16</v>
       </c>
-      <c r="AP5" s="3">
-        <v>2.5999999999999999E-2</v>
-      </c>
-      <c r="AQ5">
-        <v>0.11</v>
+      <c r="AQ5" s="4">
+        <v>6.5100000000000005E-2</v>
       </c>
       <c r="AR5">
+        <v>0.19500000000000001</v>
+      </c>
+      <c r="AS5">
         <v>21</v>
       </c>
-      <c r="AS5" s="3">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="AT5">
-        <v>0.26700000000000002</v>
-      </c>
-    </row>
-    <row r="6" spans="1:46" x14ac:dyDescent="0.3">
-      <c r="A6" s="13">
+      <c r="AT5" s="4">
+        <v>0.188</v>
+      </c>
+      <c r="AU5" s="10">
+        <v>0.35599999999999998</v>
+      </c>
+      <c r="AV5">
+        <v>31</v>
+      </c>
+      <c r="AW5" s="4">
+        <v>1.0660000000000001</v>
+      </c>
+      <c r="AX5">
+        <v>1.3009999999999999</v>
+      </c>
+      <c r="AY5">
+        <v>41</v>
+      </c>
+      <c r="AZ5" s="1">
+        <v>6.3890000000000002</v>
+      </c>
+      <c r="BA5" s="4">
+        <v>3.1259999999999999</v>
+      </c>
+      <c r="BB5">
+        <v>51</v>
+      </c>
+      <c r="BC5" s="1">
+        <v>22.23</v>
+      </c>
+      <c r="BD5" s="4">
+        <v>5.6660000000000004</v>
+      </c>
+      <c r="BE5">
+        <v>61</v>
+      </c>
+      <c r="BF5" s="10">
+        <v>64.63</v>
+      </c>
+      <c r="BG5" s="4">
+        <v>10.029999999999999</v>
+      </c>
+      <c r="BH5">
+        <v>101</v>
+      </c>
+      <c r="BI5" s="10"/>
+      <c r="BJ5" s="4">
+        <v>48.83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <v>3</v>
       </c>
       <c r="B6">
@@ -843,380 +1019,397 @@
       <c r="C6" s="6">
         <v>5.4000000000000003E-3</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="9">
         <v>1E-3</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="3"/>
+      <c r="F6">
         <v>10</v>
       </c>
-      <c r="F6" s="6">
+      <c r="G6" s="6">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="G6" s="7">
+      <c r="H6" s="9">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="11"/>
+      <c r="J6">
         <v>15</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="12">
         <v>1.67E-2</v>
       </c>
-      <c r="K6">
+      <c r="L6" s="4">
         <v>2.1899999999999999E-2</v>
       </c>
-      <c r="L6">
+      <c r="M6" s="11">
         <v>4.7E-2</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>21</v>
       </c>
-      <c r="N6" s="3">
+      <c r="O6" s="4">
         <v>2.76E-2</v>
       </c>
-      <c r="O6">
+      <c r="P6" s="11">
         <v>0.1421</v>
       </c>
-      <c r="P6">
+      <c r="Q6" s="10">
         <v>6.3E-2</v>
       </c>
-      <c r="Q6">
+      <c r="R6" s="2">
         <v>28</v>
       </c>
-      <c r="R6" s="3">
+      <c r="S6" s="4">
         <v>4.87E-2</v>
       </c>
-      <c r="S6" s="2">
+      <c r="T6" s="13">
         <v>1.03</v>
       </c>
-      <c r="T6" s="2">
+      <c r="U6" s="14">
         <v>0.1</v>
       </c>
-      <c r="U6">
+      <c r="V6">
         <v>36</v>
       </c>
-      <c r="V6" s="3">
-        <v>7.1400000000000005E-2</v>
-      </c>
-      <c r="W6">
-        <v>11.55</v>
-      </c>
-      <c r="X6">
-        <v>0.14599999999999999</v>
-      </c>
-      <c r="Y6">
+      <c r="W6" s="4">
+        <v>4.2900000000000001E-2</v>
+      </c>
+      <c r="X6" s="11">
+        <v>10.4</v>
+      </c>
+      <c r="Y6" s="10">
+        <v>0.215</v>
+      </c>
+      <c r="Z6">
         <v>55</v>
       </c>
-      <c r="Z6" s="3">
+      <c r="AA6" s="4">
         <v>0.11799999999999999</v>
       </c>
-      <c r="AB6">
+      <c r="AB6" s="11">
+        <v>118.63</v>
+      </c>
+      <c r="AC6" s="10">
         <v>0.254</v>
       </c>
-      <c r="AC6">
+      <c r="AD6">
         <v>55</v>
       </c>
-      <c r="AD6" s="3">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="AE6">
-        <v>0.33</v>
-      </c>
-      <c r="AF6">
+      <c r="AE6" s="4">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="AF6" s="10">
+        <v>0.36</v>
+      </c>
+      <c r="AG6">
         <v>66</v>
       </c>
-      <c r="AG6" s="3">
-        <v>0.25800000000000001</v>
-      </c>
-      <c r="AH6">
-        <v>0.43</v>
-      </c>
-      <c r="AI6">
+      <c r="AH6" s="4">
+        <v>0.14249999999999999</v>
+      </c>
+      <c r="AI6" s="16">
+        <v>0.47</v>
+      </c>
+      <c r="AJ6">
         <v>78</v>
       </c>
-      <c r="AJ6" s="3">
-        <v>0.436</v>
-      </c>
-      <c r="AK6">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="AL6">
+      <c r="AK6" s="4">
+        <v>0.223</v>
+      </c>
+      <c r="AL6" s="10">
+        <v>0.58499999999999996</v>
+      </c>
+      <c r="AM6">
         <v>91</v>
       </c>
-      <c r="AM6" s="3">
-        <v>0.57199999999999995</v>
-      </c>
-      <c r="AN6">
-        <v>0.74</v>
-      </c>
-      <c r="AO6">
+      <c r="AN6" s="4">
+        <v>0.34949999999999998</v>
+      </c>
+      <c r="AO6" s="10">
+        <v>0.83099999999999996</v>
+      </c>
+      <c r="AP6">
         <v>136</v>
       </c>
-      <c r="AP6" s="11">
-        <v>2.39</v>
-      </c>
-      <c r="AQ6">
-        <v>2.3199999999999998</v>
+      <c r="AQ6" s="4">
+        <v>1.87</v>
       </c>
       <c r="AR6">
+        <v>2.25</v>
+      </c>
+      <c r="AS6">
         <v>231</v>
       </c>
-      <c r="AS6" s="3">
-        <v>15.2</v>
-      </c>
-      <c r="AT6" s="11">
-        <v>21.44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:46" x14ac:dyDescent="0.3">
-      <c r="A7" s="13">
+      <c r="AT6" s="1">
+        <v>13.89</v>
+      </c>
+      <c r="AU6" s="4">
+        <v>6.22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <v>4</v>
       </c>
       <c r="B7">
         <v>10</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="7">
         <v>7.1000000000000004E-3</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="9">
         <v>1.4E-3</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="3"/>
+      <c r="F7">
         <v>20</v>
       </c>
-      <c r="F7" s="6">
+      <c r="G7" s="6">
         <v>2.0500000000000001E-2</v>
       </c>
-      <c r="G7" s="7">
+      <c r="H7" s="9">
         <v>4.1000000000000003E-3</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="11"/>
+      <c r="J7" s="2">
         <v>35</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="12">
         <v>5.1200000000000002E-2</v>
       </c>
-      <c r="K7" s="4">
+      <c r="L7" s="4">
         <v>3.8699999999999998E-2</v>
       </c>
-      <c r="L7">
+      <c r="M7" s="11">
         <v>0.14000000000000001</v>
       </c>
-      <c r="M7">
+      <c r="N7" s="2">
         <v>56</v>
       </c>
-      <c r="N7" s="3">
+      <c r="O7" s="4">
         <v>0.108</v>
       </c>
-      <c r="O7">
+      <c r="P7" s="11">
         <v>0.35399999999999998</v>
       </c>
-      <c r="P7">
+      <c r="Q7" s="10">
         <v>0.21299999999999999</v>
       </c>
-      <c r="Q7">
+      <c r="R7">
         <v>84</v>
       </c>
-      <c r="R7" s="3">
+      <c r="S7" s="4">
         <v>0.22</v>
       </c>
-      <c r="S7">
+      <c r="T7" s="11">
         <v>3.18</v>
       </c>
-      <c r="T7">
+      <c r="U7" s="12">
         <v>0.28999999999999998</v>
       </c>
-      <c r="U7">
+      <c r="V7" s="2">
         <v>120</v>
       </c>
-      <c r="V7" s="3">
-        <v>0.41699999999999998</v>
-      </c>
-      <c r="W7">
-        <v>39.46</v>
-      </c>
-      <c r="X7">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="Y7">
+      <c r="W7" s="4">
+        <v>0.221</v>
+      </c>
+      <c r="X7" s="11">
+        <v>35.22</v>
+      </c>
+      <c r="Y7" s="10">
+        <v>0.6502</v>
+      </c>
+      <c r="Z7">
         <v>165</v>
       </c>
-      <c r="Z7">
-        <v>0.94</v>
-      </c>
-      <c r="AB7" s="10">
-        <v>0.87</v>
-      </c>
-      <c r="AC7">
+      <c r="AA7" s="4">
+        <v>0.51200000000000001</v>
+      </c>
+      <c r="AB7" s="11"/>
+      <c r="AC7" s="10">
+        <v>0.94399999999999995</v>
+      </c>
+      <c r="AD7">
         <v>220</v>
       </c>
-      <c r="AD7">
-        <v>2.4700000000000002</v>
-      </c>
       <c r="AE7" s="10">
-        <v>1.51</v>
-      </c>
-      <c r="AF7">
+        <v>1.72</v>
+      </c>
+      <c r="AF7" s="4">
+        <v>1.49</v>
+      </c>
+      <c r="AG7">
         <v>286</v>
       </c>
-      <c r="AG7">
-        <v>6.91</v>
-      </c>
-      <c r="AH7" s="10">
-        <v>2.08</v>
-      </c>
-      <c r="AI7">
+      <c r="AH7" s="16">
+        <v>5.4349999999999996</v>
+      </c>
+      <c r="AI7" s="4">
+        <v>2.6819999999999999</v>
+      </c>
+      <c r="AJ7">
         <v>364</v>
       </c>
-      <c r="AJ7">
-        <v>12.94</v>
-      </c>
-      <c r="AK7" s="10">
-        <v>3.15</v>
-      </c>
-      <c r="AL7">
+      <c r="AK7" s="16">
+        <v>8.41</v>
+      </c>
+      <c r="AL7" s="4">
+        <v>3.27</v>
+      </c>
+      <c r="AM7">
         <v>455</v>
       </c>
-      <c r="AM7">
-        <v>27.8</v>
-      </c>
       <c r="AN7" s="10">
-        <v>4.29</v>
-      </c>
-      <c r="AO7">
+        <v>19.5</v>
+      </c>
+      <c r="AO7" s="4">
+        <v>5.15</v>
+      </c>
+      <c r="AP7">
         <v>816</v>
       </c>
-      <c r="AP7">
+      <c r="AQ7">
         <v>247.3</v>
       </c>
-      <c r="AQ7" s="10">
+      <c r="AR7" s="4">
         <v>13.9</v>
       </c>
-      <c r="AR7">
+      <c r="AS7">
         <v>1771</v>
       </c>
-      <c r="AT7" s="10">
-        <v>103.8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:46" x14ac:dyDescent="0.3">
-      <c r="A8" s="13">
+      <c r="AT7" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="AU7" s="4">
+        <v>55.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <v>5</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="2">
         <v>15</v>
       </c>
       <c r="C8" s="6">
         <v>1.12E-2</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="9">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="8">
+        <v>4.1399999999999999E-2</v>
+      </c>
+      <c r="F8" s="2">
         <v>35</v>
       </c>
-      <c r="F8" s="6">
+      <c r="G8" s="6">
         <v>4.3099999999999999E-2</v>
       </c>
-      <c r="G8" s="7">
+      <c r="H8" s="9">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="11"/>
+      <c r="J8">
         <v>70</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="12">
         <v>0.13</v>
       </c>
-      <c r="K8" s="5">
+      <c r="L8" s="4">
         <v>7.5899999999999995E-2</v>
       </c>
-      <c r="L8">
+      <c r="M8" s="11">
         <v>0.218</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>126</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="4">
         <v>0.32400000000000001</v>
       </c>
-      <c r="O8">
+      <c r="P8" s="11">
         <v>0.76400000000000001</v>
       </c>
-      <c r="P8">
+      <c r="Q8" s="10">
         <v>0.4</v>
       </c>
-      <c r="Q8">
+      <c r="R8" s="2">
         <v>210</v>
       </c>
-      <c r="R8" s="11">
-        <v>0.95</v>
-      </c>
-      <c r="S8">
-        <v>8.98</v>
-      </c>
-      <c r="T8" s="10">
-        <v>0.71</v>
-      </c>
-      <c r="U8">
+      <c r="S8" s="4">
+        <v>0.54469999999999996</v>
+      </c>
+      <c r="T8" s="11">
+        <v>7.9615</v>
+      </c>
+      <c r="U8" s="12">
+        <v>0.999</v>
+      </c>
+      <c r="V8">
         <v>330</v>
       </c>
-      <c r="V8" s="11">
-        <v>4.28</v>
-      </c>
-      <c r="W8">
-        <v>113.35</v>
-      </c>
-      <c r="X8" s="10">
-        <v>1.64</v>
-      </c>
-      <c r="Y8">
+      <c r="W8" s="10">
+        <v>3.34</v>
+      </c>
+      <c r="X8" s="11">
+        <v>104.39</v>
+      </c>
+      <c r="Y8" s="4">
+        <v>1.94</v>
+      </c>
+      <c r="Z8">
         <v>495</v>
       </c>
-      <c r="Z8">
-        <v>20</v>
-      </c>
-      <c r="AB8" s="10">
-        <v>2.83</v>
-      </c>
-      <c r="AC8">
+      <c r="AA8" s="10">
+        <v>15.97</v>
+      </c>
+      <c r="AB8" s="11"/>
+      <c r="AC8" s="4">
+        <v>3.19</v>
+      </c>
+      <c r="AD8">
         <v>715</v>
       </c>
-      <c r="AD8">
-        <v>47.6</v>
-      </c>
       <c r="AE8" s="10">
-        <v>5.25</v>
-      </c>
-      <c r="AF8">
+        <v>32.979999999999997</v>
+      </c>
+      <c r="AF8" s="4">
+        <v>5.38</v>
+      </c>
+      <c r="AG8">
         <v>1001</v>
       </c>
-      <c r="AG8">
-        <v>160.30000000000001</v>
-      </c>
-      <c r="AH8" s="10">
-        <v>8.65</v>
-      </c>
-      <c r="AI8">
+      <c r="AH8" s="16">
+        <v>125.54</v>
+      </c>
+      <c r="AI8" s="4">
+        <v>9.92</v>
+      </c>
+      <c r="AJ8">
         <v>1365</v>
       </c>
-      <c r="AK8" s="10">
+      <c r="AK8" s="16"/>
+      <c r="AL8" s="4">
         <v>14.7</v>
       </c>
-      <c r="AL8">
+      <c r="AM8">
         <v>1820</v>
       </c>
-      <c r="AN8" s="10">
+      <c r="AN8" s="10"/>
+      <c r="AO8" s="4">
         <v>23.6</v>
       </c>
-      <c r="AO8">
+      <c r="AP8">
         <v>3876</v>
       </c>
-      <c r="AQ8" s="10">
+      <c r="AR8" s="4">
         <v>88.2</v>
       </c>
-      <c r="AT8" s="11"/>
-    </row>
-    <row r="9" spans="1:46" x14ac:dyDescent="0.3">
-      <c r="A9" s="13">
+    </row>
+    <row r="9" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <v>6</v>
       </c>
       <c r="B9">
@@ -1225,100 +1418,109 @@
       <c r="C9" s="6">
         <v>1.5800000000000002E-2</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="9">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="3"/>
+      <c r="F9">
         <v>56</v>
       </c>
-      <c r="F9" s="6">
+      <c r="G9" s="6">
         <v>8.5099999999999995E-2</v>
       </c>
-      <c r="G9" s="7">
+      <c r="H9" s="9">
         <v>9.5999999999999992E-3</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="11"/>
+      <c r="J9">
         <v>126</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="12">
         <v>0.26300000000000001</v>
       </c>
-      <c r="K9" s="5">
+      <c r="L9" s="4">
         <v>0.14899999999999999</v>
       </c>
-      <c r="L9">
+      <c r="M9" s="11">
         <v>0.36599999999999999</v>
       </c>
-      <c r="M9">
+      <c r="N9" s="2">
         <v>252</v>
       </c>
-      <c r="N9" s="11">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="O9">
-        <v>1.53</v>
-      </c>
-      <c r="P9" s="10">
-        <v>0.75</v>
-      </c>
-      <c r="Q9">
+      <c r="O9" s="4">
+        <v>0.68059999999999998</v>
+      </c>
+      <c r="P9" s="11">
+        <v>1.4370000000000001</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>0.8639</v>
+      </c>
+      <c r="R9">
         <v>462</v>
       </c>
-      <c r="R9" s="11">
-        <v>7.6616999999999997</v>
-      </c>
-      <c r="S9">
-        <v>21.265000000000001</v>
-      </c>
-      <c r="T9" s="10">
-        <v>1.6</v>
-      </c>
-      <c r="U9">
+      <c r="S9" s="10">
+        <v>6.4260000000000002</v>
+      </c>
+      <c r="T9" s="11">
+        <v>20.440000000000001</v>
+      </c>
+      <c r="U9" s="4">
+        <v>2.23</v>
+      </c>
+      <c r="V9" s="2">
         <v>792</v>
       </c>
-      <c r="V9" s="11">
+      <c r="W9" s="10">
         <v>34.006</v>
       </c>
-      <c r="W9">
+      <c r="X9" s="11">
         <v>325.22000000000003</v>
       </c>
-      <c r="X9" s="10">
+      <c r="Y9" s="4">
         <v>6.12</v>
       </c>
-      <c r="Y9">
+      <c r="Z9">
         <v>1287</v>
       </c>
-      <c r="AB9" s="10">
+      <c r="AA9" s="10">
+        <v>137.47</v>
+      </c>
+      <c r="AB9" s="11"/>
+      <c r="AC9" s="4">
         <v>9.65</v>
       </c>
-      <c r="AC9">
+      <c r="AD9">
         <v>2002</v>
       </c>
-      <c r="AE9" s="10">
+      <c r="AE9" s="10"/>
+      <c r="AF9" s="4">
         <v>20.9</v>
       </c>
-      <c r="AF9">
+      <c r="AG9">
         <v>3003</v>
       </c>
-      <c r="AH9" s="10">
+      <c r="AH9" s="10"/>
+      <c r="AI9" s="4">
         <v>36.5</v>
       </c>
-      <c r="AI9">
+      <c r="AJ9">
         <v>4368</v>
       </c>
-      <c r="AK9" s="10">
+      <c r="AK9" s="16"/>
+      <c r="AL9" s="4">
         <v>69.900000000000006</v>
       </c>
-      <c r="AL9">
+      <c r="AM9">
         <v>6188</v>
       </c>
-      <c r="AN9" s="10">
+      <c r="AN9" s="10"/>
+      <c r="AO9" s="4">
         <v>97.4</v>
       </c>
-      <c r="AQ9" s="11"/>
-    </row>
-    <row r="10" spans="1:46" x14ac:dyDescent="0.3">
-      <c r="A10" s="13">
+    </row>
+    <row r="10" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <v>7</v>
       </c>
       <c r="B10">
@@ -1327,87 +1529,93 @@
       <c r="C10" s="6">
         <v>2.1499999999999998E-2</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="9">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="3"/>
+      <c r="F10">
         <v>84</v>
       </c>
-      <c r="F10" s="6">
+      <c r="G10" s="6">
         <v>0.1157</v>
       </c>
-      <c r="G10" s="7">
+      <c r="H10" s="9">
         <v>1.3100000000000001E-2</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="11"/>
+      <c r="J10">
         <v>210</v>
       </c>
-      <c r="J10">
-        <v>0.62111000000000005</v>
-      </c>
-      <c r="K10" s="5">
-        <v>0.25330000000000003</v>
-      </c>
-      <c r="L10">
-        <v>0.499</v>
-      </c>
-      <c r="M10">
+      <c r="K10" s="12">
+        <v>0.376</v>
+      </c>
+      <c r="L10" s="4">
+        <v>0.2273</v>
+      </c>
+      <c r="M10" s="11">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="N10">
         <v>462</v>
       </c>
-      <c r="N10">
-        <v>5.29</v>
-      </c>
       <c r="O10" s="11">
-        <v>3.13</v>
+        <v>4.16</v>
       </c>
       <c r="P10" s="10">
-        <v>1.3</v>
-      </c>
-      <c r="Q10">
+        <v>2.89</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>1.5820000000000001</v>
+      </c>
+      <c r="R10" s="2">
         <v>924</v>
       </c>
-      <c r="R10" s="11">
-        <v>40.203000000000003</v>
-      </c>
-      <c r="S10">
-        <v>47.798999999999999</v>
-      </c>
-      <c r="T10" s="10">
-        <v>3.86</v>
-      </c>
-      <c r="U10">
+      <c r="S10" s="10">
+        <v>33.61</v>
+      </c>
+      <c r="T10" s="11">
+        <v>45.2</v>
+      </c>
+      <c r="U10" s="4">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="V10">
         <v>1716</v>
       </c>
-      <c r="V10" s="11">
+      <c r="W10" s="10">
         <v>277.56</v>
       </c>
-      <c r="W10">
+      <c r="X10" s="11">
         <v>853.62</v>
       </c>
-      <c r="X10" s="10">
+      <c r="Y10" s="4">
         <v>14.2</v>
       </c>
-      <c r="Y10">
+      <c r="Z10">
         <v>3003</v>
       </c>
-      <c r="AB10" s="10">
+      <c r="AA10" s="10"/>
+      <c r="AB10" s="11"/>
+      <c r="AC10" s="4">
         <v>26.1</v>
       </c>
-      <c r="AC10">
+      <c r="AD10">
         <v>5005</v>
       </c>
-      <c r="AE10" s="10">
+      <c r="AE10" s="10"/>
+      <c r="AF10" s="4">
         <v>62.3</v>
       </c>
-      <c r="AF10">
+      <c r="AG10">
         <v>8008</v>
       </c>
-      <c r="AH10" s="10">
+      <c r="AH10" s="16"/>
+      <c r="AI10" s="4">
         <v>115.9</v>
       </c>
     </row>
-    <row r="11" spans="1:46" x14ac:dyDescent="0.3">
-      <c r="A11" s="13">
+    <row r="11" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <v>8</v>
       </c>
       <c r="B11">
@@ -1416,78 +1624,86 @@
       <c r="C11" s="6">
         <v>2.9399999999999999E-2</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="9">
         <v>3.5000000000000001E-3</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="3"/>
+      <c r="F11">
         <v>120</v>
       </c>
-      <c r="F11" s="6">
+      <c r="G11" s="6">
         <v>0.21490000000000001</v>
       </c>
-      <c r="G11" s="8">
+      <c r="H11" s="9">
         <v>1.9570000000000001E-2</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="11"/>
+      <c r="J11" s="2">
         <v>330</v>
       </c>
-      <c r="J11">
-        <v>1.5874999999999999</v>
-      </c>
-      <c r="K11" s="5">
-        <v>0.42159999999999997</v>
-      </c>
-      <c r="L11">
-        <v>0.93799999999999994</v>
-      </c>
-      <c r="M11">
+      <c r="K11" s="12">
+        <v>1.0437000000000001</v>
+      </c>
+      <c r="L11" s="4">
+        <v>0.38119999999999998</v>
+      </c>
+      <c r="M11" s="11">
+        <v>1.085</v>
+      </c>
+      <c r="N11" s="2">
         <v>792</v>
       </c>
-      <c r="N11">
+      <c r="O11" s="11">
         <v>25.300999999999998</v>
       </c>
-      <c r="O11" s="11">
+      <c r="P11" s="10">
         <v>7.5</v>
       </c>
-      <c r="P11" s="10">
+      <c r="Q11" s="4">
         <v>2.6</v>
       </c>
-      <c r="Q11">
+      <c r="R11">
         <v>1716</v>
       </c>
-      <c r="R11">
-        <v>215.24600000000001</v>
-      </c>
       <c r="S11" s="11">
-        <v>125.14</v>
+        <v>177.65</v>
       </c>
       <c r="T11" s="10">
-        <v>7.77</v>
-      </c>
-      <c r="U11">
+        <v>120.75</v>
+      </c>
+      <c r="U11" s="4">
+        <v>9.06</v>
+      </c>
+      <c r="V11" s="2">
         <v>3432</v>
       </c>
-      <c r="W11">
-        <v>2812.4</v>
-      </c>
-      <c r="X11" s="10">
-        <v>27.6</v>
-      </c>
-      <c r="Y11">
+      <c r="W11" s="10">
+        <v>2061.1999999999998</v>
+      </c>
+      <c r="X11" s="11">
+        <v>3018</v>
+      </c>
+      <c r="Y11" s="4">
+        <v>25.22</v>
+      </c>
+      <c r="Z11">
         <v>6435</v>
       </c>
-      <c r="AB11" s="10">
+      <c r="AA11" s="10"/>
+      <c r="AB11" s="11"/>
+      <c r="AC11" s="4">
         <v>66.3</v>
       </c>
-      <c r="AF11">
+      <c r="AG11">
         <v>19448</v>
       </c>
-      <c r="AH11" s="10">
+      <c r="AH11" s="16"/>
+      <c r="AI11" s="4">
         <v>350.9</v>
       </c>
     </row>
-    <row r="12" spans="1:46" x14ac:dyDescent="0.3">
-      <c r="A12" s="13">
+    <row r="12" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
         <v>9</v>
       </c>
       <c r="B12">
@@ -1496,125 +1712,140 @@
       <c r="C12" s="6">
         <v>4.0599999999999997E-2</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="9">
         <v>4.4000000000000003E-3</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="3"/>
+      <c r="F12">
         <v>165</v>
       </c>
-      <c r="F12" s="6">
+      <c r="G12" s="6">
         <v>0.33289999999999997</v>
       </c>
-      <c r="G12" s="8">
+      <c r="H12" s="9">
         <v>3.032E-2</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="11"/>
+      <c r="J12">
         <v>495</v>
       </c>
-      <c r="J12">
-        <v>4.2747999999999999</v>
-      </c>
-      <c r="K12" s="5">
-        <v>0.65849999999999997</v>
-      </c>
-      <c r="L12">
-        <v>1.52</v>
-      </c>
-      <c r="M12">
+      <c r="K12" s="11">
+        <v>3.524</v>
+      </c>
+      <c r="L12" s="4">
+        <v>0.62849999999999995</v>
+      </c>
+      <c r="M12" s="12">
+        <v>1.65</v>
+      </c>
+      <c r="N12">
         <v>1287</v>
       </c>
-      <c r="N12">
+      <c r="O12" s="11">
         <v>67.19</v>
       </c>
-      <c r="O12" s="11">
+      <c r="P12" s="10">
         <v>14.7</v>
       </c>
-      <c r="P12" s="10">
+      <c r="Q12" s="4">
         <v>4.6500000000000004</v>
       </c>
-      <c r="Q12" s="11">
+      <c r="R12" s="2">
         <v>3003</v>
       </c>
+      <c r="S12" s="11">
+        <v>863.4</v>
+      </c>
       <c r="T12" s="10">
+        <v>302.60000000000002</v>
+      </c>
+      <c r="U12" s="4">
         <v>19.2</v>
       </c>
-      <c r="U12">
+      <c r="V12">
         <v>6435</v>
       </c>
-      <c r="X12" s="10">
+      <c r="Y12" s="4">
         <v>54.4</v>
       </c>
     </row>
-    <row r="13" spans="1:46" x14ac:dyDescent="0.3">
-      <c r="A13" s="13">
+    <row r="13" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
         <v>10</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="2">
         <v>55</v>
       </c>
       <c r="C13" s="6">
         <v>5.74E-2</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="9">
         <v>5.5999999999999999E-3</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="8">
+        <v>0.18559999999999999</v>
+      </c>
+      <c r="F13" s="2">
         <v>220</v>
       </c>
-      <c r="F13" s="6">
-        <v>0.59260000000000002</v>
-      </c>
-      <c r="G13" s="8">
+      <c r="G13" s="6">
+        <v>0.41799999999999998</v>
+      </c>
+      <c r="H13" s="9">
         <v>4.6249999999999999E-2</v>
       </c>
-      <c r="H13">
-        <v>0.68</v>
-      </c>
-      <c r="I13">
+      <c r="I13" s="11">
+        <v>0.72899999999999998</v>
+      </c>
+      <c r="J13">
         <v>715</v>
       </c>
-      <c r="J13">
+      <c r="K13" s="11">
         <v>13.308999999999999</v>
       </c>
-      <c r="K13" s="5">
+      <c r="L13" s="4">
         <v>1.085</v>
       </c>
-      <c r="L13">
+      <c r="M13" s="12">
         <v>2.86</v>
       </c>
-      <c r="M13">
+      <c r="N13" s="2">
         <v>2002</v>
       </c>
-      <c r="N13">
+      <c r="O13" s="11">
         <v>250.82</v>
       </c>
-      <c r="O13" s="11">
+      <c r="P13" s="10">
         <v>28.6</v>
       </c>
-      <c r="P13" s="10">
+      <c r="Q13" s="4">
         <v>8.4</v>
       </c>
-      <c r="Q13" s="11">
+      <c r="R13" s="15">
         <v>5005</v>
       </c>
+      <c r="S13" s="11"/>
       <c r="T13" s="10">
+        <v>742.1</v>
+      </c>
+      <c r="U13" s="4">
         <v>41.7</v>
       </c>
-      <c r="U13">
+      <c r="V13">
         <v>11440</v>
       </c>
-      <c r="X13" s="10">
+      <c r="Y13" s="4">
         <v>102.4</v>
       </c>
-      <c r="AF13">
+      <c r="AG13">
         <v>92378</v>
       </c>
-      <c r="AH13" s="10">
-        <v>4203</v>
-      </c>
-    </row>
-    <row r="14" spans="1:46" x14ac:dyDescent="0.3">
-      <c r="A14" s="13">
+      <c r="AI13" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
         <v>11</v>
       </c>
       <c r="B14">
@@ -1623,42 +1854,58 @@
       <c r="C14" s="6">
         <v>7.5800000000000006E-2</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="9">
         <v>6.8999999999999999E-3</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="3"/>
+      <c r="F14">
         <v>286</v>
       </c>
-      <c r="F14" s="6">
-        <v>0.99350000000000005</v>
-      </c>
-      <c r="G14" s="8">
+      <c r="G14" s="6">
+        <v>0.69740000000000002</v>
+      </c>
+      <c r="H14" s="9">
         <v>8.1699999999999995E-2</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="11">
+        <v>1.0129999999999999</v>
+      </c>
+      <c r="J14">
         <v>1001</v>
       </c>
-      <c r="J14">
+      <c r="K14" s="11">
         <v>32.71</v>
       </c>
-      <c r="K14" s="5">
+      <c r="L14" s="4">
         <v>1.9019999999999999</v>
       </c>
-      <c r="L14">
+      <c r="M14" s="12">
         <v>3.91</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>3003</v>
       </c>
       <c r="O14" s="11">
+        <v>682.3</v>
+      </c>
+      <c r="P14" s="10">
         <v>82.7</v>
       </c>
-      <c r="P14" s="10">
+      <c r="Q14" s="4">
         <v>18.8</v>
       </c>
-    </row>
-    <row r="15" spans="1:46" x14ac:dyDescent="0.3">
-      <c r="A15" s="13">
+      <c r="R14">
+        <v>8008</v>
+      </c>
+      <c r="T14" s="10">
+        <v>2312.5</v>
+      </c>
+      <c r="U14" s="4">
+        <v>66.540000000000006</v>
+      </c>
+    </row>
+    <row r="15" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
         <v>12</v>
       </c>
       <c r="B15">
@@ -1667,39 +1914,46 @@
       <c r="C15" s="6">
         <v>9.0399999999999994E-2</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="9">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="3"/>
+      <c r="F15">
         <v>364</v>
       </c>
-      <c r="F15" s="6">
-        <v>1.6571</v>
-      </c>
       <c r="G15" s="8">
+        <v>1.2339</v>
+      </c>
+      <c r="H15" s="9">
         <v>0.11219999999999999</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="10">
+        <v>1.1919999999999999</v>
+      </c>
+      <c r="J15" s="2">
         <v>1365</v>
       </c>
-      <c r="J15">
+      <c r="K15" s="11">
         <v>73.959999999999994</v>
       </c>
-      <c r="K15" s="5">
+      <c r="L15" s="4">
         <v>3.46</v>
       </c>
-      <c r="L15">
+      <c r="M15" s="12">
         <v>5.33</v>
       </c>
-      <c r="M15">
+      <c r="N15" s="2">
         <v>4368</v>
       </c>
       <c r="P15" s="10">
+        <v>119.6</v>
+      </c>
+      <c r="Q15" s="4">
         <v>31.6</v>
       </c>
     </row>
-    <row r="16" spans="1:46" x14ac:dyDescent="0.3">
-      <c r="A16" s="13">
+    <row r="16" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
         <v>13</v>
       </c>
       <c r="B16">
@@ -1708,39 +1962,46 @@
       <c r="C16" s="6">
         <v>0.1171</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="9">
         <v>9.2999999999999992E-3</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="3"/>
+      <c r="F16">
         <v>455</v>
       </c>
-      <c r="F16" s="6">
-        <v>2.9605999999999999</v>
-      </c>
       <c r="G16" s="8">
+        <v>2.266</v>
+      </c>
+      <c r="H16" s="9">
         <v>0.1575</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="10">
+        <v>1.7050000000000001</v>
+      </c>
+      <c r="J16">
         <v>1820</v>
       </c>
-      <c r="J16">
+      <c r="K16" s="11">
         <v>163.63999999999999</v>
       </c>
-      <c r="K16" s="5">
+      <c r="L16" s="4">
         <v>5.97</v>
       </c>
-      <c r="L16">
+      <c r="M16" s="12">
         <v>8.8699999999999992</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>6188</v>
       </c>
       <c r="P16" s="10">
-        <v>51.6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="13">
+        <v>267.14999999999998</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>40.19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
         <v>14</v>
       </c>
       <c r="B17">
@@ -1749,68 +2010,94 @@
       <c r="C17" s="6">
         <v>0.1527</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="9">
         <v>1.11E-2</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="3"/>
+      <c r="F17">
         <v>560</v>
       </c>
-      <c r="F17" s="6">
+      <c r="G17" s="8">
         <v>5.4229000000000003</v>
       </c>
-      <c r="G17" s="8">
+      <c r="H17" s="9">
         <v>0.2472</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="10"/>
+      <c r="J17">
         <v>2380</v>
       </c>
-      <c r="J17">
+      <c r="K17" s="11">
         <v>361.35</v>
       </c>
-      <c r="K17" s="5">
-        <v>10.62</v>
-      </c>
-      <c r="L17" s="11">
-        <v>13.4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="13">
+      <c r="L17" s="4">
+        <v>8.7370000000000001</v>
+      </c>
+      <c r="M17" s="12">
+        <v>10.538</v>
+      </c>
+      <c r="N17" s="2">
+        <v>8568</v>
+      </c>
+      <c r="P17" s="10">
+        <v>537.66</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>56.41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
         <v>15</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="2">
         <v>120</v>
       </c>
       <c r="C18" s="6">
         <v>0.19040000000000001</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="9">
         <v>1.3299999999999999E-2</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="8">
+        <v>0.45519999999999999</v>
+      </c>
+      <c r="F18" s="2">
         <v>680</v>
       </c>
-      <c r="F18" s="6">
+      <c r="G18" s="8">
         <v>10.016</v>
       </c>
-      <c r="G18" s="8">
+      <c r="H18" s="9">
         <v>0.33639999999999998</v>
       </c>
-      <c r="H18">
+      <c r="I18" s="10">
         <v>2.88</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>3060</v>
       </c>
-      <c r="K18" s="5">
-        <v>17.420000000000002</v>
-      </c>
-      <c r="L18" s="11">
-        <v>18.2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="13">
+      <c r="K18" s="11">
+        <v>636.96</v>
+      </c>
+      <c r="L18" s="4">
+        <v>15.02</v>
+      </c>
+      <c r="M18" s="12">
+        <v>15.26</v>
+      </c>
+      <c r="N18">
+        <v>11628</v>
+      </c>
+      <c r="P18" s="10">
+        <v>1097.7</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>92.97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
         <v>16</v>
       </c>
       <c r="B19">
@@ -1819,30 +2106,32 @@
       <c r="C19" s="6">
         <v>0.24349999999999999</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="9">
         <v>1.6E-2</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="3"/>
+      <c r="F19">
         <v>816</v>
       </c>
-      <c r="F19" s="6">
+      <c r="G19" s="8">
         <v>17.59</v>
       </c>
-      <c r="G19" s="8">
+      <c r="H19" s="9">
         <v>0.47720000000000001</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="10"/>
+      <c r="J19" s="2">
         <v>3876</v>
       </c>
-      <c r="K19" s="5">
-        <v>29.8</v>
-      </c>
-      <c r="L19" s="11">
-        <v>30.4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="13">
+      <c r="L19" s="12">
+        <v>26.03</v>
+      </c>
+      <c r="M19" s="4">
+        <v>20.82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
         <v>17</v>
       </c>
       <c r="B20">
@@ -1851,30 +2140,32 @@
       <c r="C20" s="6">
         <v>0.30330000000000001</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="9">
         <v>1.8800000000000001E-2</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="3"/>
+      <c r="F20">
         <v>969</v>
       </c>
-      <c r="F20" s="6">
+      <c r="G20" s="8">
         <v>30.295999999999999</v>
       </c>
-      <c r="G20" s="8">
+      <c r="H20" s="9">
         <v>0.68389999999999995</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="10"/>
+      <c r="J20">
         <v>4845</v>
       </c>
-      <c r="K20" s="11">
-        <v>57.6</v>
-      </c>
-      <c r="L20" s="10">
-        <v>45.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="13">
+      <c r="L20" s="12">
+        <v>47.06</v>
+      </c>
+      <c r="M20" s="4">
+        <v>29.9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
         <v>18</v>
       </c>
       <c r="B21">
@@ -1883,30 +2174,32 @@
       <c r="C21" s="6">
         <v>0.36969999999999997</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="9">
         <v>2.2700000000000001E-2</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="3"/>
+      <c r="F21">
         <v>1140</v>
       </c>
-      <c r="F21" s="6">
+      <c r="G21" s="8">
         <v>52.107999999999997</v>
       </c>
-      <c r="G21" s="8">
+      <c r="H21" s="9">
         <v>0.96730000000000005</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="10"/>
+      <c r="J21">
         <v>5985</v>
       </c>
-      <c r="K21" s="11">
-        <v>87.3</v>
-      </c>
-      <c r="L21" s="10">
-        <v>61.1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="13">
+      <c r="L21" s="12">
+        <v>82.9</v>
+      </c>
+      <c r="M21" s="4">
+        <v>40.76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
         <v>19</v>
       </c>
       <c r="B22">
@@ -1915,613 +2208,439 @@
       <c r="C22" s="6">
         <v>0.47320000000000001</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="9">
         <v>2.6499999999999999E-2</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="3"/>
+      <c r="F22">
         <v>1330</v>
       </c>
-      <c r="F22" s="6">
+      <c r="G22" s="8">
         <v>85.512</v>
       </c>
-      <c r="G22" s="8">
+      <c r="H22" s="9">
         <v>1.4261999999999999</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="13">
+      <c r="I22" s="10"/>
+      <c r="J22">
+        <v>7315</v>
+      </c>
+      <c r="L22" s="10">
+        <v>143.72</v>
+      </c>
+      <c r="M22" s="4">
+        <v>53.68</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
         <v>20</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="2">
         <v>210</v>
       </c>
       <c r="C23" s="6">
         <v>0.58850000000000002</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="9">
         <v>3.0300000000000001E-2</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="8">
+        <v>1.0791999999999999</v>
+      </c>
+      <c r="F23" s="2">
         <v>1540</v>
       </c>
-      <c r="F23" s="6">
+      <c r="G23" s="8">
         <v>111.59</v>
       </c>
-      <c r="G23" s="8">
+      <c r="H23" s="9">
         <v>1.9286000000000001</v>
       </c>
-      <c r="H23">
+      <c r="I23" s="10">
         <v>10.42</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="13">
+      <c r="J23">
+        <v>8855</v>
+      </c>
+      <c r="L23" s="10">
+        <v>284.22000000000003</v>
+      </c>
+      <c r="M23" s="4">
+        <v>70.48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A24" s="5"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="I24" s="10"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
         <v>25</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="2">
         <v>325</v>
       </c>
       <c r="C25" s="6">
         <v>1.7762</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="9">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="8">
+        <v>1.8776999999999999</v>
+      </c>
+      <c r="F25" s="2">
         <v>2925</v>
       </c>
       <c r="G25" s="8">
-        <v>10.38</v>
-      </c>
-      <c r="H25">
-        <v>38.4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="13">
+        <v>679.6</v>
+      </c>
+      <c r="H25" s="9">
+        <v>8.91</v>
+      </c>
+      <c r="I25" s="10">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A26" s="5">
         <v>30</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="2">
         <v>465</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="8">
         <v>4.3099999999999996</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="9">
         <v>0.1197</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="6">
+        <v>3.3641999999999999</v>
+      </c>
+      <c r="F26" s="2">
         <v>4960</v>
       </c>
-      <c r="G26" s="8">
-        <v>45.3</v>
-      </c>
-      <c r="H26">
-        <v>84.4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="13">
+      <c r="H26" s="9">
+        <v>38.04</v>
+      </c>
+      <c r="I26" s="10">
+        <v>50.43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A27" s="5">
         <v>35</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="2">
         <v>630</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="8">
         <v>11.242000000000001</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="9">
         <v>0.22370000000000001</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="6">
+        <v>5.8926999999999996</v>
+      </c>
+      <c r="F27" s="2">
         <v>7770</v>
       </c>
-      <c r="G27" s="8">
-        <v>149.69999999999999</v>
-      </c>
-      <c r="H27">
-        <v>212.7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="13">
+      <c r="H27" s="6">
+        <v>125.16</v>
+      </c>
+      <c r="I27" s="4">
+        <v>108.44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A28" s="5">
         <v>40</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="2">
         <v>820</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="8">
         <v>24.498000000000001</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="9">
         <v>0.3654</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="6">
+        <v>10.06</v>
+      </c>
+      <c r="F28" s="2">
         <v>11480</v>
       </c>
-      <c r="G28" s="12">
-        <v>509.5</v>
-      </c>
-      <c r="H28" s="10">
-        <v>361.3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="13">
+      <c r="H28" s="6">
+        <v>370.4</v>
+      </c>
+      <c r="I28" s="4">
+        <v>192.76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A29" s="5">
         <v>45</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="2">
         <v>1035</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="8">
         <v>52.857999999999997</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="9">
         <v>0.59060000000000001</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="13">
+      <c r="E29" s="6">
+        <v>14.856</v>
+      </c>
+      <c r="F29" s="2">
+        <v>16215</v>
+      </c>
+      <c r="H29" s="10">
+        <v>1086.02</v>
+      </c>
+      <c r="I29" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A30" s="5">
         <v>50</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="2">
         <v>1275</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="8">
         <v>110.31</v>
       </c>
-      <c r="D30" s="8">
+      <c r="D30" s="9">
         <v>0.92769999999999997</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="13">
+      <c r="E30" s="6">
+        <v>22.384</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A31" s="5">
         <v>55</v>
       </c>
       <c r="B31">
         <v>1540</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="8">
         <v>205.82</v>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="9">
         <v>1.4283999999999999</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="13">
+      <c r="E31" s="3"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A32" s="5">
         <v>60</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="2">
         <v>1830</v>
       </c>
-      <c r="C32" s="6">
-        <v>393.27</v>
-      </c>
-      <c r="D32" s="8">
-        <v>2.3026</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="11"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="11"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="11"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="11"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="11"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="11"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="11"/>
-      <c r="B38" s="11"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="11"/>
-      <c r="I38" s="11"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="11"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="11"/>
-      <c r="B39" s="11"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="11"/>
-      <c r="I39" s="11"/>
-      <c r="J39" s="11"/>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11"/>
-      <c r="M39" s="11"/>
-      <c r="N39" s="11"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="11"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="11"/>
-      <c r="I40" s="11"/>
-      <c r="J40" s="11"/>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="11"/>
-      <c r="N40" s="11"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="11"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="11"/>
-      <c r="J41" s="11"/>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
-      <c r="M41" s="11"/>
-      <c r="N41" s="11"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="11"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="11"/>
-      <c r="I42" s="11"/>
-      <c r="J42" s="11"/>
-      <c r="K42" s="11"/>
-      <c r="L42" s="11"/>
-      <c r="M42" s="11"/>
-      <c r="N42" s="11"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="11"/>
-      <c r="B43" s="11"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
-      <c r="I43" s="11"/>
-      <c r="J43" s="11"/>
-      <c r="K43" s="11"/>
-      <c r="L43" s="11"/>
-      <c r="M43" s="11"/>
-      <c r="N43" s="11"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="11"/>
-      <c r="B44" s="11"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
-      <c r="I44" s="11"/>
-      <c r="J44" s="11"/>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="11"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="11"/>
-      <c r="B45" s="11"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="11"/>
-      <c r="H45" s="11"/>
-      <c r="I45" s="11"/>
-      <c r="J45" s="11"/>
-      <c r="K45" s="11"/>
-      <c r="L45" s="11"/>
-      <c r="M45" s="11"/>
-      <c r="N45" s="11"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="11"/>
-      <c r="B46" s="11"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="11"/>
-      <c r="I46" s="11"/>
-      <c r="J46" s="11"/>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="11"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="11"/>
-      <c r="B47" s="11"/>
-      <c r="C47" s="12"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="11"/>
-      <c r="F47" s="11"/>
-      <c r="G47" s="11"/>
-      <c r="H47" s="11"/>
-      <c r="I47" s="11"/>
-      <c r="J47" s="11"/>
-      <c r="K47" s="11"/>
-      <c r="L47" s="11"/>
-      <c r="M47" s="11"/>
-      <c r="N47" s="11"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="11"/>
-      <c r="B48" s="11"/>
-      <c r="C48" s="12"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="11"/>
-      <c r="G48" s="11"/>
-      <c r="H48" s="11"/>
-      <c r="I48" s="11"/>
-      <c r="J48" s="11"/>
-      <c r="K48" s="11"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="11"/>
-      <c r="N48" s="11"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="11"/>
-      <c r="B49" s="11"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="11"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="11"/>
-      <c r="H49" s="11"/>
-      <c r="I49" s="11"/>
-      <c r="J49" s="11"/>
-      <c r="K49" s="11"/>
-      <c r="L49" s="11"/>
-      <c r="M49" s="11"/>
-      <c r="N49" s="11"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="11"/>
-      <c r="B50" s="11"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="12"/>
-      <c r="E50" s="11"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="11"/>
-      <c r="H50" s="11"/>
-      <c r="I50" s="11"/>
-      <c r="J50" s="11"/>
-      <c r="K50" s="11"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="11"/>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="11"/>
-      <c r="B51" s="11"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="11"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="11"/>
-      <c r="H51" s="11"/>
-      <c r="I51" s="11"/>
-      <c r="J51" s="11"/>
-      <c r="K51" s="11"/>
-      <c r="L51" s="11"/>
-      <c r="M51" s="11"/>
-      <c r="N51" s="11"/>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="11"/>
-      <c r="B52" s="11"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="12"/>
-      <c r="E52" s="11"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="11"/>
-      <c r="H52" s="11"/>
-      <c r="I52" s="11"/>
-      <c r="J52" s="11"/>
-      <c r="K52" s="11"/>
-      <c r="L52" s="11"/>
-      <c r="M52" s="11"/>
-      <c r="N52" s="11"/>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="11"/>
-      <c r="B53" s="11"/>
-      <c r="C53" s="12"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="11"/>
-      <c r="F53" s="11"/>
-      <c r="G53" s="11"/>
-      <c r="H53" s="11"/>
-      <c r="I53" s="11"/>
-      <c r="J53" s="11"/>
-      <c r="K53" s="11"/>
-      <c r="L53" s="11"/>
-      <c r="M53" s="11"/>
-      <c r="N53" s="11"/>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="11"/>
-      <c r="B54" s="11"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="12"/>
-      <c r="E54" s="11"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="11"/>
-      <c r="H54" s="11"/>
-      <c r="I54" s="11"/>
-      <c r="J54" s="11"/>
-      <c r="K54" s="11"/>
-      <c r="L54" s="11"/>
-      <c r="M54" s="11"/>
-      <c r="N54" s="11"/>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="11"/>
-      <c r="B55" s="11"/>
-      <c r="C55" s="12"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="11"/>
-      <c r="F55" s="11"/>
-      <c r="G55" s="11"/>
-      <c r="H55" s="11"/>
-      <c r="I55" s="11"/>
-      <c r="J55" s="11"/>
-      <c r="K55" s="11"/>
-      <c r="L55" s="11"/>
-      <c r="M55" s="11"/>
-      <c r="N55" s="11"/>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="11"/>
-      <c r="B56" s="11"/>
-      <c r="C56" s="12"/>
-      <c r="D56" s="12"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="11"/>
-      <c r="H56" s="11"/>
-      <c r="I56" s="11"/>
-      <c r="J56" s="11"/>
-      <c r="K56" s="11"/>
-      <c r="L56" s="11"/>
-      <c r="M56" s="11"/>
-      <c r="N56" s="11"/>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="11"/>
-      <c r="B57" s="11"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="12"/>
-      <c r="E57" s="11"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="11"/>
-      <c r="H57" s="11"/>
-      <c r="I57" s="11"/>
-      <c r="J57" s="11"/>
-      <c r="K57" s="11"/>
-      <c r="L57" s="11"/>
-      <c r="M57" s="11"/>
-      <c r="N57" s="11"/>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="11"/>
-      <c r="B58" s="11"/>
-      <c r="C58" s="12"/>
-      <c r="D58" s="12"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="11"/>
-      <c r="H58" s="11"/>
-      <c r="I58" s="11"/>
-      <c r="J58" s="11"/>
-      <c r="K58" s="11"/>
-      <c r="L58" s="11"/>
-      <c r="M58" s="11"/>
-      <c r="N58" s="11"/>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="11"/>
-      <c r="B59" s="11"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="12"/>
-      <c r="E59" s="11"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="11"/>
-      <c r="H59" s="11"/>
-      <c r="I59" s="11"/>
-      <c r="J59" s="11"/>
-      <c r="K59" s="11"/>
-      <c r="L59" s="11"/>
-      <c r="M59" s="11"/>
-      <c r="N59" s="11"/>
+      <c r="C32" s="8">
+        <v>441.88</v>
+      </c>
+      <c r="D32" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="E32" s="6">
+        <v>47.697000000000003</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="5">
+        <v>70</v>
+      </c>
+      <c r="B33">
+        <v>2485</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" s="9">
+        <v>6.234</v>
+      </c>
+      <c r="E33" s="6">
+        <v>93.001000000000005</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="5">
+        <v>80</v>
+      </c>
+      <c r="B34" s="2">
+        <v>3240</v>
+      </c>
+      <c r="D34" s="9">
+        <v>12.49</v>
+      </c>
+      <c r="E34" s="6">
+        <v>158.82</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="5">
+        <v>90</v>
+      </c>
+      <c r="B35">
+        <v>4095</v>
+      </c>
+      <c r="D35" s="9">
+        <v>23.88</v>
+      </c>
+      <c r="E35" s="6">
+        <v>266.63</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="5">
+        <v>100</v>
+      </c>
+      <c r="B36">
+        <v>5050</v>
+      </c>
+      <c r="D36" s="9">
+        <v>40.64</v>
+      </c>
+      <c r="E36" s="6">
+        <v>450.76</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="5">
+        <v>150</v>
+      </c>
+      <c r="B37">
+        <v>11325</v>
+      </c>
+      <c r="D37" s="9">
+        <v>381.69</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+    </row>
+    <row r="49" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+    </row>
+    <row r="50" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+    </row>
+    <row r="51" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+    </row>
+    <row r="52" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+    </row>
+    <row r="53" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+    </row>
+    <row r="54" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+    </row>
+    <row r="55" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+    </row>
+    <row r="56" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+    </row>
+    <row r="57" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+    </row>
+    <row r="58" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+    </row>
+    <row r="59" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
